--- a/Output/ranking_toto_gol.xlsx
+++ b/Output/ranking_toto_gol.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,20 +454,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gandalf</t>
+          <t>Demo2</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -476,174 +476,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Goku</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Maria</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Pedro</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Scooby Doo</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Vegueta</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Gladiador</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Output/ranking_toto_gol.xlsx
+++ b/Output/ranking_toto_gol.xlsx
@@ -467,7 +467,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -489,7 +489,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
